--- a/令和9年度_行事・テスト時数一覧.xlsx
+++ b/令和9年度_行事・テスト時数一覧.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="行事・テスト一覧" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R9時数見込み" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前年度の名残（要修正）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前年度の名残（修正済み）" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1日すべて事前指導とみなした（要確認）</t>
+          <t>1〜3限。4〜6限は授業</t>
         </is>
       </c>
     </row>
@@ -2512,47 +2512,44 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46819</v>
+        <v>46815</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>卒業式</t>
+          <t>卒業式練習</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
           <t>行事</t>
         </is>
-      </c>
-      <c r="F74" t="n">
-        <v>3</v>
       </c>
       <c r="G74" t="n">
         <v>3</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>カウントでは2年は3/7に授業が入り、3/3が空き（前年度の日付のまま）</t>
+          <t>1〜3限</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46825</v>
+        <v>46819</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>立会演説会</t>
+          <t>卒業式</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2560,26 +2557,30 @@
           <t>行事</t>
         </is>
       </c>
-      <c r="E75" t="n">
-        <v>1</v>
-      </c>
       <c r="F75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3時数</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46835</v>
+        <v>46825</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>大掃除</t>
+          <t>立会演説会</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2588,6 +2589,9 @@
         </is>
       </c>
       <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -2603,7 +2607,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>集会</t>
+          <t>大掃除</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2611,60 +2615,84 @@
           <t>行事</t>
         </is>
       </c>
-      <c r="F77" t="n">
+      <c r="E77" t="n">
         <v>1</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
+        <v>46835</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>集会</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>行事</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
         <v>46836</v>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>式</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>行事</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>行事</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr"/>
-      <c r="C80" s="3" t="inlineStr"/>
-      <c r="D80" s="3" t="inlineStr"/>
-      <c r="E80" s="3">
-        <f>SUM(E2:E78)</f>
+      <c r="B81" s="3" t="inlineStr"/>
+      <c r="C81" s="3" t="inlineStr"/>
+      <c r="D81" s="3" t="inlineStr"/>
+      <c r="E81" s="3">
+        <f>SUM(E2:E79)</f>
         <v/>
       </c>
-      <c r="F80" s="3">
-        <f>SUM(F2:F78)</f>
+      <c r="F81" s="3">
+        <f>SUM(F2:F79)</f>
         <v/>
       </c>
-      <c r="G80" s="3">
-        <f>SUM(G2:G78)</f>
+      <c r="G81" s="3">
+        <f>SUM(G2:G79)</f>
         <v/>
       </c>
-      <c r="H80" s="3" t="n"/>
+      <c r="H81" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2721,13 +2749,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>936</v>
+        <v>950</v>
       </c>
       <c r="C2" t="n">
-        <v>925</v>
+        <v>939</v>
       </c>
       <c r="D2" t="n">
-        <v>806</v>
+        <v>833</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2876,7 +2904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2905,7 +2933,7 @@
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>空いているコマ</t>
+          <t>空いていたコマ</t>
         </is>
       </c>
       <c r="E1" s="5" t="inlineStr">
@@ -2915,7 +2943,7 @@
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
-          <t>令和9年度の年計</t>
+          <t>対応</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2971,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>授業に戻した</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2999,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4/30に⑤⑥進路説明会（カウントでは4/30は授業）</t>
+          <t>授業に戻した</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3029,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>授業に戻した</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3057,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>なし（実力テスト①は年計にない）</t>
+          <t>授業に戻した</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3087,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>授業に戻した</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3117,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>授業に戻した</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3145,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>授業に戻した</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3173,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>授業に戻した</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3201,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>授業に戻した</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3231,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>授業に戻した</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3259,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>なし（令和9年度も行うなら行事に数える）</t>
+          <t>未定のため空けたまま</t>
         </is>
       </c>
     </row>
@@ -3259,37 +3287,65 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>未定のため空けたまま</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
+        <v>46545</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1〜6限</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>修学旅行事前指導</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1〜3限を事前指導、4〜6限を授業にした</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
         <v>46815</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>1・2年</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>1〜6限</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>卒業式（R8の日付）</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>卒業式は3/7。カウントの3/3と3/7を入れ替える必要あり</t>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>3/3は授業、3/7は1年家庭学習日・2年卒業式に入れ替えた</t>
         </is>
       </c>
     </row>

--- a/令和9年度_行事・テスト時数一覧.xlsx
+++ b/令和9年度_行事・テスト時数一覧.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>行事</t>
+          <t>総合</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2140,67 +2140,72 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46743</v>
+        <v>46710</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>大掃除</t>
+          <t>未来マップ（総合）</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>行事</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>総合</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>5・6限。総合として数える</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46743</v>
+        <v>46734</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>集会</t>
+          <t>未来マップ（総合）</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>行事</t>
+          <t>総合</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>5・6限。総合として数える</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46744</v>
+        <v>46743</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>式</t>
+          <t>大掃除</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2208,29 +2213,23 @@
           <t>行事</t>
         </is>
       </c>
-      <c r="E62" t="n">
-        <v>1</v>
-      </c>
       <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="n">
         <v>1</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46759</v>
+        <v>46743</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>式</t>
+          <t>集会</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2239,9 +2238,6 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
@@ -2251,16 +2247,16 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46771</v>
+        <v>46744</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>職場体験(2年)</t>
+          <t>式</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2268,23 +2264,29 @@
           <t>行事</t>
         </is>
       </c>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
       <c r="F64" t="n">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46772</v>
+        <v>46759</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>職場体験(2年)</t>
+          <t>式</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2292,38 +2294,44 @@
           <t>行事</t>
         </is>
       </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46776</v>
+        <v>46771</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>実力テスト(3年)</t>
+          <t>職場体験(2年)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>テスト</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>5</v>
+          <t>行事</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>6</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46800</v>
+        <v>46772</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2332,34 +2340,31 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>学年末テスト</t>
+          <t>職場体験(2年)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>テスト</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>3</v>
+          <t>行事</t>
+        </is>
       </c>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46801</v>
+        <v>46776</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>学年末テスト</t>
+          <t>実力テスト(3年)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2367,110 +2372,107 @@
           <t>テスト</t>
         </is>
       </c>
-      <c r="E68" t="n">
-        <v>3</v>
-      </c>
-      <c r="F68" t="n">
-        <v>3</v>
+      <c r="G68" t="n">
+        <v>5</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46811</v>
+        <v>46800</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>3送会準備・リハ</t>
+          <t>学年末テスト</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>行事</t>
+          <t>テスト</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
-      </c>
-      <c r="G69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46812</v>
+        <v>46801</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>3年生を送る会</t>
+          <t>学年末テスト</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>行事</t>
+          <t>テスト</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46813</v>
+        <v>46811</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>卒業式練習</t>
+          <t>3送会準備・リハ</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>行事</t>
         </is>
+      </c>
+      <c r="E71" t="n">
+        <v>2</v>
       </c>
       <c r="F71" t="n">
         <v>2</v>
       </c>
+      <c r="G71" t="n">
+        <v>2</v>
+      </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46814</v>
+        <v>46812</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>卒業式準備</t>
+          <t>3年生を送る会</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2482,17 +2484,20 @@
         <v>1</v>
       </c>
       <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
         <v>1</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46814</v>
+        <v>46813</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2506,22 +2511,22 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46815</v>
+        <v>46814</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>卒業式練習</t>
+          <t>卒業式準備</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2529,27 +2534,26 @@
           <t>行事</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>3</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>1〜3限</t>
-        </is>
-      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46819</v>
+        <v>46814</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>卒業式</t>
+          <t>卒業式練習</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2558,29 +2562,22 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
-      </c>
-      <c r="G75" t="n">
-        <v>3</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>3時数</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46825</v>
+        <v>46815</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>立会演説会</t>
+          <t>卒業式練習</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2588,26 +2585,27 @@
           <t>行事</t>
         </is>
       </c>
-      <c r="E76" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="n">
+        <v>3</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>1〜3限</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46835</v>
+        <v>46819</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>大掃除</t>
+          <t>卒業式</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2615,29 +2613,39 @@
           <t>行事</t>
         </is>
       </c>
-      <c r="E77" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" t="n">
+        <v>3</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>3時数</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46835</v>
+        <v>46825</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>集会</t>
+          <t>立会演説会</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>行事</t>
         </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
@@ -2646,53 +2654,101 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
+        <v>46835</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>大掃除</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>行事</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46835</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>集会</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>行事</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
         <v>46836</v>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>式</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>行事</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>行事</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr"/>
-      <c r="C81" s="3" t="inlineStr"/>
-      <c r="D81" s="3" t="inlineStr"/>
-      <c r="E81" s="3">
-        <f>SUM(E2:E79)</f>
+      <c r="B83" s="3" t="inlineStr"/>
+      <c r="C83" s="3" t="inlineStr"/>
+      <c r="D83" s="3" t="inlineStr"/>
+      <c r="E83" s="3">
+        <f>SUM(E2:E81)</f>
         <v/>
       </c>
-      <c r="F81" s="3">
-        <f>SUM(F2:F79)</f>
+      <c r="F83" s="3">
+        <f>SUM(F2:F81)</f>
         <v/>
       </c>
-      <c r="G81" s="3">
-        <f>SUM(G2:G79)</f>
+      <c r="G83" s="3">
+        <f>SUM(G2:G81)</f>
         <v/>
       </c>
-      <c r="H81" s="3" t="n"/>
+      <c r="H83" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2794,7 +2850,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>115</v>
@@ -3259,7 +3315,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>未定のため空けたまま</t>
+          <t>実施。総合として数える</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3343,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>未定のため空けたまま</t>
+          <t>実施。総合として数える</t>
         </is>
       </c>
     </row>
